--- a/Packages/cn.etetet.childrenmgr/Luban/Config/Datas/SchoolGrade/SchoolGrade.xlsx
+++ b/Packages/cn.etetet.childrenmgr/Luban/Config/Datas/SchoolGrade/SchoolGrade.xlsx
@@ -57,7 +57,7 @@
     <t>grade_name</t>
   </si>
   <si>
-    <t>class_id</t>
+    <t>class_ids</t>
   </si>
   <si>
     <t>##type</t>
@@ -69,7 +69,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=,),int</t>
+    <t>(list#sep=,),(int#ref=SchoolGrade.GradeClassConfigCategory)</t>
   </si>
   <si>
     <t>##group</t>

--- a/Packages/cn.etetet.childrenmgr/Luban/Config/Datas/SchoolGrade/SchoolGrade.xlsx
+++ b/Packages/cn.etetet.childrenmgr/Luban/Config/Datas/SchoolGrade/SchoolGrade.xlsx
@@ -1340,7 +1340,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7">
-        <v>10001</v>
+        <v>20000</v>
       </c>
       <c r="C7" t="s">
         <v>15</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8">
-        <v>10002</v>
+        <v>30000</v>
       </c>
       <c r="C8" t="s">
         <v>17</v>
